--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_6/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7592,0.1373,0.0974,0.0127</t>
-  </si>
-  <si>
-    <t>0.8317,0.0295,0.0681,0.0290</t>
-  </si>
-  <si>
-    <t>0.9435,0.0192,0.0255,0.0021</t>
-  </si>
-  <si>
-    <t>0.9065,0.0198,0.0244,0.0095</t>
-  </si>
-  <si>
-    <t>0.9490,0.0138,0.0110,0.0044</t>
-  </si>
-  <si>
-    <t>0.9383,0.0113,0.0148,0.0096</t>
-  </si>
-  <si>
-    <t>0.9089,0.0358,0.0274,0.0071</t>
-  </si>
-  <si>
-    <t>0.9319,0.0182,0.0192,0.0071</t>
-  </si>
-  <si>
-    <t>0.9378,0.0177,0.0100,0.0082</t>
-  </si>
-  <si>
-    <t>0.9405,0.0196,0.0157,0.0047</t>
-  </si>
-  <si>
-    <t>0.9345,0.0203,0.0143,0.0066</t>
-  </si>
-  <si>
-    <t>0.9354,0.0244,0.0057,0.0063</t>
-  </si>
-  <si>
-    <t>0.8606,0.0514,0.0859,0.0045</t>
-  </si>
-  <si>
-    <t>0.2610,0.2020,0.5624,0.0055</t>
-  </si>
-  <si>
-    <t>0.7441,0.0109,0.4406,0.0021</t>
-  </si>
-  <si>
-    <t>0.7792,0.0409,0.2282,0.0033</t>
-  </si>
-  <si>
-    <t>0.8473,0.0654,0.0841,0.0064</t>
-  </si>
-  <si>
-    <t>0.4214,0.5865,0.0776,0.0246</t>
-  </si>
-  <si>
-    <t>0.1832,0.8092,0.0644,0.0222</t>
-  </si>
-  <si>
-    <t>0.6782,0.2634,0.0635,0.0158</t>
-  </si>
-  <si>
-    <t>0.5204,0.4425,0.0714,0.0147</t>
-  </si>
-  <si>
-    <t>0.2766,0.7110,0.1315,0.0209</t>
-  </si>
-  <si>
-    <t>0.8810,0.0200,0.1524,0.0022</t>
-  </si>
-  <si>
-    <t>0.8132,0.0369,0.2127,0.0034</t>
-  </si>
-  <si>
-    <t>0.5435,0.0369,0.5344,0.0026</t>
-  </si>
-  <si>
-    <t>0.7027,0.0634,0.2911,0.0043</t>
-  </si>
-  <si>
-    <t>0.8059,0.0104,0.3168,0.0019</t>
-  </si>
-  <si>
-    <t>0.8408,0.0222,0.1919,0.0018</t>
-  </si>
-  <si>
-    <t>0.4523,0.0198,0.6617,0.0014</t>
-  </si>
-  <si>
-    <t>0.8909,0.0628,0.0357,0.0025</t>
-  </si>
-  <si>
-    <t>0.8379,0.0792,0.0718,0.0104</t>
-  </si>
-  <si>
-    <t>0.3050,0.0366,0.7724,0.0060</t>
-  </si>
-  <si>
-    <t>0.5412,0.3528,0.1240,0.0103</t>
-  </si>
-  <si>
-    <t>0.8706,0.0662,0.0398,0.0058</t>
-  </si>
-  <si>
-    <t>0.9202,0.0265,0.0332,0.0034</t>
-  </si>
-  <si>
-    <t>0.8948,0.0525,0.0371,0.0052</t>
-  </si>
-  <si>
-    <t>0.6218,0.2334,0.2394,0.0357</t>
-  </si>
-  <si>
-    <t>0.2534,0.2935,0.5168,0.0011</t>
-  </si>
-  <si>
-    <t>0.4015,0.0234,0.7088,0.0008</t>
-  </si>
-  <si>
-    <t>0.5896,0.0561,0.4698,0.0014</t>
-  </si>
-  <si>
-    <t>0.6182,0.0342,0.5114,0.0009</t>
-  </si>
-  <si>
-    <t>0.4845,0.0150,0.7083,0.0008</t>
-  </si>
-  <si>
-    <t>0.2548,0.4139,0.2539,0.0018</t>
-  </si>
-  <si>
-    <t>0.3416,0.0538,0.7221,0.0049</t>
-  </si>
-  <si>
-    <t>0.7657,0.1751,0.0442,0.0109</t>
-  </si>
-  <si>
-    <t>0.3321,0.5128,0.2827,0.0168</t>
-  </si>
-  <si>
-    <t>0.2642,0.4900,0.3670,0.0145</t>
-  </si>
-  <si>
-    <t>0.3052,0.5781,0.1887,0.0116</t>
-  </si>
-  <si>
-    <t>0.1409,0.0661,0.8622,0.0010</t>
-  </si>
-  <si>
-    <t>0.0768,0.3086,0.8584,0.0006</t>
-  </si>
-  <si>
-    <t>0.5311,0.0345,0.5317,0.0010</t>
-  </si>
-  <si>
-    <t>0.6249,0.0271,0.4837,0.0022</t>
-  </si>
-  <si>
-    <t>0.0408,0.0439,0.9604,0.0029</t>
-  </si>
-  <si>
-    <t>0.7454,0.0503,0.2307,0.0018</t>
-  </si>
-  <si>
-    <t>0.9377,0.0247,0.0119,0.0051</t>
-  </si>
-  <si>
-    <t>0.9326,0.0227,0.0161,0.0047</t>
-  </si>
-  <si>
-    <t>0.9369,0.0208,0.0248,0.0052</t>
-  </si>
-  <si>
-    <t>0.1460,0.1526,0.8825,0.0080</t>
-  </si>
-  <si>
-    <t>0.8980,0.0381,0.0278,0.0095</t>
-  </si>
-  <si>
-    <t>0.9306,0.0293,0.0104,0.0069</t>
-  </si>
-  <si>
-    <t>0.9455,0.0143,0.0113,0.0057</t>
-  </si>
-  <si>
-    <t>0.0199,0.7094,0.9211,0.0013</t>
-  </si>
-  <si>
-    <t>0.1689,0.0238,0.9166,0.0003</t>
-  </si>
-  <si>
-    <t>0.5636,0.0331,0.5780,0.0007</t>
-  </si>
-  <si>
-    <t>0.0147,0.5778,0.9470,0.0006</t>
-  </si>
-  <si>
-    <t>0.1046,0.0528,0.8841,0.0020</t>
-  </si>
-  <si>
-    <t>0.4858,0.4214,0.0836,0.0037</t>
-  </si>
-  <si>
-    <t>0.0629,0.9529,0.0138,0.0009</t>
-  </si>
-  <si>
-    <t>0.9096,0.0201,0.0961,0.0031</t>
-  </si>
-  <si>
-    <t>0.9096,0.0233,0.0485,0.0049</t>
-  </si>
-  <si>
-    <t>0.0921,0.0326,0.9015,0.0062</t>
-  </si>
-  <si>
-    <t>0.0768,0.6431,0.6757,0.0008</t>
-  </si>
-  <si>
-    <t>0.0273,0.7378,0.8381,0.0007</t>
-  </si>
-  <si>
-    <t>0.0154,0.8701,0.7974,0.0005</t>
-  </si>
-  <si>
-    <t>0.0238,0.7229,0.8678,0.0011</t>
-  </si>
-  <si>
-    <t>0.7939,0.0709,0.1313,0.0124</t>
-  </si>
-  <si>
-    <t>0.8891,0.0132,0.0229,0.0277</t>
-  </si>
-  <si>
-    <t>0.9119,0.0142,0.0412,0.0094</t>
-  </si>
-  <si>
-    <t>0.8835,0.0365,0.0280,0.0143</t>
-  </si>
-  <si>
-    <t>0.8969,0.0185,0.0927,0.0090</t>
-  </si>
-  <si>
-    <t>0.8796,0.0360,0.0626,0.0092</t>
-  </si>
-  <si>
-    <t>0.0492,0.5946,0.8206,0.0009</t>
-  </si>
-  <si>
-    <t>0.0064,0.9089,0.8809,0.0002</t>
-  </si>
-  <si>
-    <t>0.1711,0.0447,0.8325,0.0006</t>
-  </si>
-  <si>
-    <t>0.1531,0.2858,0.6898,0.0017</t>
-  </si>
-  <si>
-    <t>0.0930,0.3726,0.7746,0.0004</t>
-  </si>
-  <si>
-    <t>0.1301,0.5469,0.5194,0.0016</t>
-  </si>
-  <si>
-    <t>0.9598,0.0143,0.0113,0.0032</t>
-  </si>
-  <si>
-    <t>0.8561,0.0711,0.0278,0.0109</t>
-  </si>
-  <si>
-    <t>0.9282,0.0299,0.0091,0.0059</t>
-  </si>
-  <si>
-    <t>0.9218,0.0278,0.0160,0.0069</t>
-  </si>
-  <si>
-    <t>0.9336,0.0207,0.0144,0.0056</t>
-  </si>
-  <si>
-    <t>0.8945,0.0363,0.0261,0.0137</t>
-  </si>
-  <si>
-    <t>0.9483,0.0176,0.0120,0.0049</t>
-  </si>
-  <si>
-    <t>0.9540,0.0104,0.0099,0.0046</t>
-  </si>
-  <si>
-    <t>0.9385,0.0136,0.0131,0.0076</t>
-  </si>
-  <si>
-    <t>0.9300,0.0275,0.0160,0.0059</t>
-  </si>
-  <si>
-    <t>0.9346,0.0228,0.0116,0.0067</t>
-  </si>
-  <si>
-    <t>0.8899,0.0318,0.0424,0.0131</t>
-  </si>
-  <si>
-    <t>0.9140,0.0286,0.0172,0.0091</t>
-  </si>
-  <si>
-    <t>0.9396,0.0160,0.0150,0.0059</t>
-  </si>
-  <si>
-    <t>0.9613,0.0100,0.0077,0.0036</t>
-  </si>
-  <si>
-    <t>0.9278,0.0326,0.0130,0.0073</t>
-  </si>
-  <si>
-    <t>0.1660,0.0332,0.8756,0.0014</t>
-  </si>
-  <si>
-    <t>0.6329,0.0377,0.4513,0.0035</t>
-  </si>
-  <si>
-    <t>0.8752,0.0358,0.0908,0.0047</t>
-  </si>
-  <si>
-    <t>0.7806,0.0526,0.2015,0.0036</t>
-  </si>
-  <si>
-    <t>0.6294,0.3581,0.0638,0.0190</t>
-  </si>
-  <si>
-    <t>0.6473,0.2976,0.0677,0.0268</t>
-  </si>
-  <si>
-    <t>0.7377,0.2135,0.0444,0.0105</t>
-  </si>
-  <si>
-    <t>0.7547,0.1672,0.0618,0.0089</t>
-  </si>
-  <si>
-    <t>0.4216,0.5704,0.0755,0.0247</t>
-  </si>
-  <si>
-    <t>0.4230,0.5911,0.0572,0.0086</t>
-  </si>
-  <si>
-    <t>0.8941,0.0503,0.0342,0.0060</t>
-  </si>
-  <si>
-    <t>0.8800,0.0410,0.0703,0.0070</t>
-  </si>
-  <si>
-    <t>0.7007,0.1219,0.1856,0.0045</t>
-  </si>
-  <si>
-    <t>0.7704,0.0479,0.1852,0.0019</t>
-  </si>
-  <si>
-    <t>0.8142,0.0319,0.2157,0.0038</t>
-  </si>
-  <si>
-    <t>0.8040,0.0799,0.1089,0.0112</t>
-  </si>
-  <si>
-    <t>0.1007,0.8495,0.2241,0.0139</t>
-  </si>
-  <si>
-    <t>0.1447,0.8312,0.1500,0.0200</t>
-  </si>
-  <si>
-    <t>0.5807,0.3231,0.1334,0.0138</t>
-  </si>
-  <si>
-    <t>0.0023,0.7297,0.9818,0.0006</t>
-  </si>
-  <si>
-    <t>0.7188,0.1620,0.1425,0.0087</t>
-  </si>
-  <si>
-    <t>0.7233,0.2023,0.0566,0.0165</t>
-  </si>
-  <si>
-    <t>0.5539,0.4379,0.0552,0.0219</t>
-  </si>
-  <si>
-    <t>0.9464,0.0156,0.0116,0.0040</t>
-  </si>
-  <si>
-    <t>0.9469,0.0117,0.0080,0.0050</t>
-  </si>
-  <si>
-    <t>0.9288,0.0150,0.0246,0.0073</t>
-  </si>
-  <si>
-    <t>0.9325,0.0188,0.0234,0.0062</t>
-  </si>
-  <si>
-    <t>0.9360,0.0227,0.0230,0.0048</t>
-  </si>
-  <si>
-    <t>0.9121,0.0252,0.0297,0.0080</t>
-  </si>
-  <si>
-    <t>0.9429,0.0206,0.0139,0.0034</t>
-  </si>
-  <si>
-    <t>0.8948,0.0403,0.0160,0.0118</t>
-  </si>
-  <si>
-    <t>0.0260,0.6506,0.9099,0.0007</t>
-  </si>
-  <si>
-    <t>0.3865,0.1363,0.5709,0.0013</t>
-  </si>
-  <si>
-    <t>0.0961,0.3366,0.7913,0.0009</t>
-  </si>
-  <si>
-    <t>0.1741,0.3612,0.6232,0.0029</t>
-  </si>
-  <si>
-    <t>0.8994,0.0376,0.0543,0.0034</t>
-  </si>
-  <si>
-    <t>0.8558,0.0776,0.0442,0.0024</t>
-  </si>
-  <si>
-    <t>0.8487,0.0242,0.1818,0.0042</t>
-  </si>
-  <si>
-    <t>0.8406,0.0573,0.0909,0.0052</t>
-  </si>
-  <si>
-    <t>0.9014,0.0283,0.0283,0.0101</t>
-  </si>
-  <si>
-    <t>0.6969,0.0539,0.0804,0.1248</t>
-  </si>
-  <si>
-    <t>0.8549,0.0431,0.0510,0.0185</t>
-  </si>
-  <si>
-    <t>0.8559,0.0265,0.0947,0.0189</t>
-  </si>
-  <si>
-    <t>0.0114,0.7951,0.9284,0.0010</t>
-  </si>
-  <si>
-    <t>0.9327,0.0238,0.0186,0.0050</t>
-  </si>
-  <si>
-    <t>0.9158,0.0372,0.0163,0.0055</t>
-  </si>
-  <si>
-    <t>0.8899,0.0474,0.0208,0.0110</t>
-  </si>
-  <si>
-    <t>0.8884,0.0638,0.0228,0.0058</t>
-  </si>
-  <si>
-    <t>0.9534,0.0105,0.0161,0.0035</t>
-  </si>
-  <si>
-    <t>0.9262,0.0184,0.0286,0.0053</t>
-  </si>
-  <si>
-    <t>0.9468,0.0182,0.0168,0.0035</t>
-  </si>
-  <si>
-    <t>0.1640,0.0858,0.8476,0.0246</t>
-  </si>
-  <si>
-    <t>0.9370,0.0146,0.0219,0.0035</t>
-  </si>
-  <si>
-    <t>0.9156,0.0323,0.0333,0.0047</t>
-  </si>
-  <si>
-    <t>0.8197,0.0995,0.0616,0.0084</t>
-  </si>
-  <si>
-    <t>0.8758,0.0492,0.0467,0.0082</t>
-  </si>
-  <si>
-    <t>0.8991,0.0323,0.0569,0.0034</t>
-  </si>
-  <si>
-    <t>0.8593,0.0813,0.0544,0.0068</t>
-  </si>
-  <si>
-    <t>0.9010,0.0428,0.0232,0.0057</t>
-  </si>
-  <si>
-    <t>0.8769,0.0411,0.0426,0.0107</t>
-  </si>
-  <si>
-    <t>0.9014,0.0315,0.0153,0.0104</t>
-  </si>
-  <si>
-    <t>0.9063,0.0366,0.0229,0.0087</t>
-  </si>
-  <si>
-    <t>0.9523,0.0108,0.0130,0.0048</t>
-  </si>
-  <si>
-    <t>0.8791,0.0499,0.0555,0.0095</t>
-  </si>
-  <si>
-    <t>0.9683,0.0083,0.0091,0.0027</t>
-  </si>
-  <si>
-    <t>0.8970,0.0348,0.0347,0.0105</t>
-  </si>
-  <si>
-    <t>0.9336,0.0225,0.0155,0.0055</t>
-  </si>
-  <si>
-    <t>0.9085,0.0454,0.0313,0.0048</t>
-  </si>
-  <si>
-    <t>0.6880,0.2843,0.0761,0.0179</t>
-  </si>
-  <si>
-    <t>0.7764,0.1507,0.0504,0.0119</t>
-  </si>
-  <si>
-    <t>0.8927,0.0437,0.0266,0.0084</t>
-  </si>
-  <si>
-    <t>0.7987,0.1173,0.0450,0.0204</t>
-  </si>
-  <si>
-    <t>0.8777,0.0460,0.0157,0.0128</t>
-  </si>
-  <si>
-    <t>0.8142,0.1094,0.0716,0.0138</t>
-  </si>
-  <si>
-    <t>0.9156,0.0206,0.0110,0.0106</t>
-  </si>
-  <si>
-    <t>0.9336,0.0300,0.0127,0.0034</t>
-  </si>
-  <si>
-    <t>0.6186,0.0380,0.4897,0.0066</t>
-  </si>
-  <si>
-    <t>0.8765,0.0463,0.0280,0.0130</t>
-  </si>
-  <si>
-    <t>0.3196,0.0457,0.7193,0.0015</t>
-  </si>
-  <si>
-    <t>0.3340,0.0206,0.8155,0.0009</t>
-  </si>
-  <si>
-    <t>0.5959,0.0336,0.4850,0.0032</t>
-  </si>
-  <si>
-    <t>0.4274,0.0164,0.7489,0.0005</t>
-  </si>
-  <si>
-    <t>0.3368,0.0833,0.6854,0.0017</t>
-  </si>
-  <si>
-    <t>0.0876,0.0237,0.9319,0.0009</t>
-  </si>
-  <si>
-    <t>0.6721,0.0279,0.4358,0.0016</t>
-  </si>
-  <si>
-    <t>0.6694,0.1565,0.2125,0.0060</t>
-  </si>
-  <si>
-    <t>0.8142,0.0524,0.1908,0.0051</t>
-  </si>
-  <si>
-    <t>0.8427,0.0496,0.1508,0.0057</t>
-  </si>
-  <si>
-    <t>0.5583,0.2615,0.2159,0.0172</t>
-  </si>
-  <si>
-    <t>0.7603,0.1301,0.1338,0.0052</t>
-  </si>
-  <si>
-    <t>0.8084,0.0401,0.1823,0.0028</t>
-  </si>
-  <si>
-    <t>0.9086,0.0295,0.0690,0.0032</t>
-  </si>
-  <si>
-    <t>0.8178,0.0402,0.1846,0.0051</t>
-  </si>
-  <si>
-    <t>0.8566,0.0979,0.0187,0.0081</t>
-  </si>
-  <si>
-    <t>0.8134,0.1473,0.0354,0.0066</t>
-  </si>
-  <si>
-    <t>0.9105,0.0422,0.0279,0.0055</t>
-  </si>
-  <si>
-    <t>0.9148,0.0462,0.0202,0.0053</t>
-  </si>
-  <si>
-    <t>0.8734,0.0481,0.0385,0.0124</t>
-  </si>
-  <si>
-    <t>0.7429,0.1131,0.1331,0.0063</t>
-  </si>
-  <si>
-    <t>0.8160,0.0183,0.2568,0.0060</t>
-  </si>
-  <si>
-    <t>0.8501,0.0375,0.1342,0.0092</t>
-  </si>
-  <si>
-    <t>0.8520,0.0364,0.1395,0.0045</t>
-  </si>
-  <si>
-    <t>0.8298,0.0507,0.1330,0.0060</t>
-  </si>
-  <si>
-    <t>0.0188,0.0117,0.9810,0.0009</t>
-  </si>
-  <si>
-    <t>0.2920,0.2444,0.5631,0.0024</t>
-  </si>
-  <si>
-    <t>0.5880,0.0319,0.4758,0.0010</t>
-  </si>
-  <si>
-    <t>0.6053,0.0661,0.3098,0.0009</t>
-  </si>
-  <si>
-    <t>0.4864,0.1328,0.3535,0.0018</t>
-  </si>
-  <si>
-    <t>0.9075,0.0288,0.0222,0.0143</t>
-  </si>
-  <si>
-    <t>0.9115,0.0279,0.0155,0.0088</t>
-  </si>
-  <si>
-    <t>0.8793,0.0427,0.0292,0.0158</t>
-  </si>
-  <si>
-    <t>0.9021,0.0342,0.0280,0.0104</t>
-  </si>
-  <si>
-    <t>0.9228,0.0341,0.0189,0.0052</t>
-  </si>
-  <si>
-    <t>0.9063,0.0378,0.0312,0.0073</t>
-  </si>
-  <si>
-    <t>0.9475,0.0097,0.0158,0.0066</t>
-  </si>
-  <si>
-    <t>0.9298,0.0180,0.0244,0.0066</t>
-  </si>
-  <si>
-    <t>0.8436,0.0653,0.0778,0.0101</t>
-  </si>
-  <si>
-    <t>0.7762,0.1070,0.0931,0.0194</t>
-  </si>
-  <si>
-    <t>0.9191,0.0252,0.0275,0.0051</t>
-  </si>
-  <si>
-    <t>0.2066,0.0146,0.8603,0.0007</t>
-  </si>
-  <si>
-    <t>0.1210,0.1218,0.8198,0.0020</t>
-  </si>
-  <si>
-    <t>0.4571,0.2250,0.2766,0.0027</t>
-  </si>
-  <si>
-    <t>0.1769,0.0272,0.8876,0.0006</t>
-  </si>
-  <si>
-    <t>0.5995,0.0360,0.4776,0.0023</t>
-  </si>
-  <si>
-    <t>0.3275,0.0130,0.8420,0.0004</t>
-  </si>
-  <si>
-    <t>0.3301,0.0361,0.7216,0.0015</t>
-  </si>
-  <si>
-    <t>0.4097,0.1088,0.6190,0.0056</t>
-  </si>
-  <si>
-    <t>0.7410,0.0376,0.2865,0.0073</t>
-  </si>
-  <si>
-    <t>0.7716,0.0430,0.2563,0.0050</t>
-  </si>
-  <si>
-    <t>0.8460,0.0506,0.1067,0.0047</t>
-  </si>
-  <si>
-    <t>0.9254,0.0319,0.0180,0.0051</t>
-  </si>
-  <si>
-    <t>0.9219,0.0263,0.0194,0.0069</t>
-  </si>
-  <si>
-    <t>0.9251,0.0363,0.0100,0.0061</t>
-  </si>
-  <si>
-    <t>0.9425,0.0211,0.0084,0.0044</t>
-  </si>
-  <si>
-    <t>0.9625,0.0101,0.0099,0.0030</t>
-  </si>
-  <si>
-    <t>0.9402,0.0180,0.0125,0.0055</t>
-  </si>
-  <si>
-    <t>0.9295,0.0138,0.0061,0.0128</t>
-  </si>
-  <si>
-    <t>0.9460,0.0235,0.0109,0.0033</t>
-  </si>
-  <si>
-    <t>0.3709,0.2148,0.4273,0.0043</t>
-  </si>
-  <si>
-    <t>0.1806,0.2407,0.5636,0.0032</t>
-  </si>
-  <si>
-    <t>0.1462,0.1025,0.8479,0.0019</t>
-  </si>
-  <si>
-    <t>0.7269,0.0376,0.2612,0.0015</t>
-  </si>
-  <si>
-    <t>0.2116,0.0310,0.8345,0.0017</t>
-  </si>
-  <si>
-    <t>0.8439,0.0313,0.1684,0.0029</t>
-  </si>
-  <si>
-    <t>0.7791,0.0718,0.1528,0.0048</t>
-  </si>
-  <si>
-    <t>0.3795,0.0259,0.7584,0.0021</t>
-  </si>
-  <si>
-    <t>0.9401,0.0136,0.0175,0.0057</t>
-  </si>
-  <si>
-    <t>0.8272,0.0600,0.0818,0.0241</t>
-  </si>
-  <si>
-    <t>0.8784,0.0239,0.0495,0.0166</t>
-  </si>
-  <si>
-    <t>0.8520,0.0280,0.0578,0.0265</t>
-  </si>
-  <si>
-    <t>0.8337,0.0291,0.0407,0.0508</t>
-  </si>
-  <si>
-    <t>0.7160,0.1181,0.1693,0.0179</t>
+    <t>0.9100,0.0209,0.0475,0.0044</t>
+  </si>
+  <si>
+    <t>0.9086,0.0247,0.0300,0.0071</t>
+  </si>
+  <si>
+    <t>0.8752,0.0367,0.0805,0.0081</t>
+  </si>
+  <si>
+    <t>0.8656,0.0422,0.0368,0.0131</t>
+  </si>
+  <si>
+    <t>0.9321,0.0219,0.0149,0.0059</t>
+  </si>
+  <si>
+    <t>0.9220,0.0259,0.0233,0.0069</t>
+  </si>
+  <si>
+    <t>0.8839,0.0430,0.0355,0.0144</t>
+  </si>
+  <si>
+    <t>0.9181,0.0282,0.0200,0.0097</t>
+  </si>
+  <si>
+    <t>0.9079,0.0328,0.0222,0.0095</t>
+  </si>
+  <si>
+    <t>0.8809,0.0404,0.0192,0.0152</t>
+  </si>
+  <si>
+    <t>0.8977,0.0340,0.0189,0.0133</t>
+  </si>
+  <si>
+    <t>0.9463,0.0158,0.0225,0.0040</t>
+  </si>
+  <si>
+    <t>0.5707,0.3012,0.1840,0.0226</t>
+  </si>
+  <si>
+    <t>0.7611,0.0691,0.1986,0.0074</t>
+  </si>
+  <si>
+    <t>0.8365,0.0320,0.1800,0.0042</t>
+  </si>
+  <si>
+    <t>0.7429,0.0179,0.3780,0.0033</t>
+  </si>
+  <si>
+    <t>0.8647,0.0440,0.1036,0.0041</t>
+  </si>
+  <si>
+    <t>0.6927,0.2771,0.0542,0.0127</t>
+  </si>
+  <si>
+    <t>0.6106,0.3155,0.0740,0.0064</t>
+  </si>
+  <si>
+    <t>0.8726,0.0620,0.0303,0.0068</t>
+  </si>
+  <si>
+    <t>0.5640,0.3551,0.0903,0.0161</t>
+  </si>
+  <si>
+    <t>0.2066,0.8056,0.0975,0.0219</t>
+  </si>
+  <si>
+    <t>0.8012,0.0334,0.2638,0.0063</t>
+  </si>
+  <si>
+    <t>0.8142,0.0289,0.2504,0.0032</t>
+  </si>
+  <si>
+    <t>0.5976,0.0133,0.5953,0.0007</t>
+  </si>
+  <si>
+    <t>0.5478,0.0717,0.4237,0.0046</t>
+  </si>
+  <si>
+    <t>0.7166,0.0635,0.2768,0.0048</t>
+  </si>
+  <si>
+    <t>0.7270,0.0358,0.3133,0.0040</t>
+  </si>
+  <si>
+    <t>0.4597,0.0234,0.6222,0.0014</t>
+  </si>
+  <si>
+    <t>0.7539,0.1776,0.0629,0.0100</t>
+  </si>
+  <si>
+    <t>0.8494,0.0611,0.0747,0.0060</t>
+  </si>
+  <si>
+    <t>0.1299,0.0266,0.9257,0.0019</t>
+  </si>
+  <si>
+    <t>0.5858,0.1245,0.3050,0.0059</t>
+  </si>
+  <si>
+    <t>0.8522,0.0706,0.0453,0.0086</t>
+  </si>
+  <si>
+    <t>0.8982,0.0194,0.1115,0.0039</t>
+  </si>
+  <si>
+    <t>0.7889,0.1544,0.0348,0.0141</t>
+  </si>
+  <si>
+    <t>0.8042,0.1219,0.0745,0.0125</t>
+  </si>
+  <si>
+    <t>0.4666,0.1930,0.3244,0.0008</t>
+  </si>
+  <si>
+    <t>0.4549,0.0268,0.6597,0.0006</t>
+  </si>
+  <si>
+    <t>0.5924,0.0480,0.4661,0.0008</t>
+  </si>
+  <si>
+    <t>0.5411,0.0744,0.4796,0.0021</t>
+  </si>
+  <si>
+    <t>0.3793,0.0140,0.7797,0.0006</t>
+  </si>
+  <si>
+    <t>0.1557,0.7562,0.0948,0.0028</t>
+  </si>
+  <si>
+    <t>0.5272,0.0480,0.4970,0.0021</t>
+  </si>
+  <si>
+    <t>0.7420,0.1559,0.0761,0.0094</t>
+  </si>
+  <si>
+    <t>0.2230,0.7663,0.1267,0.0145</t>
+  </si>
+  <si>
+    <t>0.2283,0.7414,0.0756,0.0029</t>
+  </si>
+  <si>
+    <t>0.4076,0.4087,0.2300,0.0065</t>
+  </si>
+  <si>
+    <t>0.0529,0.2214,0.8877,0.0007</t>
+  </si>
+  <si>
+    <t>0.2027,0.1078,0.7793,0.0022</t>
+  </si>
+  <si>
+    <t>0.6178,0.0628,0.3238,0.0016</t>
+  </si>
+  <si>
+    <t>0.6742,0.0316,0.3539,0.0013</t>
+  </si>
+  <si>
+    <t>0.4524,0.0710,0.5956,0.0036</t>
+  </si>
+  <si>
+    <t>0.4361,0.0499,0.5885,0.0030</t>
+  </si>
+  <si>
+    <t>0.8749,0.0613,0.0228,0.0105</t>
+  </si>
+  <si>
+    <t>0.9359,0.0135,0.0145,0.0077</t>
+  </si>
+  <si>
+    <t>0.9040,0.0358,0.0272,0.0074</t>
+  </si>
+  <si>
+    <t>0.6116,0.0370,0.4868,0.0034</t>
+  </si>
+  <si>
+    <t>0.9094,0.0287,0.0200,0.0093</t>
+  </si>
+  <si>
+    <t>0.9191,0.0339,0.0208,0.0055</t>
+  </si>
+  <si>
+    <t>0.8491,0.0883,0.0399,0.0102</t>
+  </si>
+  <si>
+    <t>0.1589,0.4273,0.6172,0.0008</t>
+  </si>
+  <si>
+    <t>0.1794,0.1034,0.8620,0.0004</t>
+  </si>
+  <si>
+    <t>0.1188,0.2818,0.8635,0.0014</t>
+  </si>
+  <si>
+    <t>0.0099,0.7860,0.9176,0.0003</t>
+  </si>
+  <si>
+    <t>0.1349,0.0384,0.8764,0.0008</t>
+  </si>
+  <si>
+    <t>0.3892,0.4917,0.1568,0.0059</t>
+  </si>
+  <si>
+    <t>0.0377,0.9688,0.0357,0.0020</t>
+  </si>
+  <si>
+    <t>0.8282,0.0629,0.1450,0.0103</t>
+  </si>
+  <si>
+    <t>0.8866,0.0286,0.0726,0.0082</t>
+  </si>
+  <si>
+    <t>0.0489,0.0348,0.9360,0.0124</t>
+  </si>
+  <si>
+    <t>0.0066,0.9594,0.4761,0.0002</t>
+  </si>
+  <si>
+    <t>0.1112,0.4317,0.7123,0.0009</t>
+  </si>
+  <si>
+    <t>0.0108,0.8980,0.8220,0.0003</t>
+  </si>
+  <si>
+    <t>0.0135,0.8254,0.9136,0.0003</t>
+  </si>
+  <si>
+    <t>0.8539,0.0353,0.0709,0.0147</t>
+  </si>
+  <si>
+    <t>0.8961,0.0316,0.0288,0.0113</t>
+  </si>
+  <si>
+    <t>0.9109,0.0242,0.0285,0.0087</t>
+  </si>
+  <si>
+    <t>0.8854,0.0314,0.0361,0.0186</t>
+  </si>
+  <si>
+    <t>0.8451,0.0374,0.0827,0.0154</t>
+  </si>
+  <si>
+    <t>0.7981,0.0404,0.0685,0.0543</t>
+  </si>
+  <si>
+    <t>0.0278,0.7815,0.7816,0.0012</t>
+  </si>
+  <si>
+    <t>0.2512,0.1206,0.7234,0.0006</t>
+  </si>
+  <si>
+    <t>0.1769,0.3202,0.5281,0.0011</t>
+  </si>
+  <si>
+    <t>0.0243,0.2386,0.9575,0.0004</t>
+  </si>
+  <si>
+    <t>0.0367,0.4847,0.8761,0.0004</t>
+  </si>
+  <si>
+    <t>0.2197,0.3720,0.4583,0.0014</t>
+  </si>
+  <si>
+    <t>0.9087,0.0265,0.0190,0.0139</t>
+  </si>
+  <si>
+    <t>0.8978,0.0534,0.0334,0.0059</t>
+  </si>
+  <si>
+    <t>0.9307,0.0336,0.0173,0.0046</t>
+  </si>
+  <si>
+    <t>0.8924,0.0480,0.0330,0.0069</t>
+  </si>
+  <si>
+    <t>0.9167,0.0219,0.0161,0.0112</t>
+  </si>
+  <si>
+    <t>0.9195,0.0301,0.0232,0.0079</t>
+  </si>
+  <si>
+    <t>0.9399,0.0209,0.0235,0.0043</t>
+  </si>
+  <si>
+    <t>0.8878,0.0578,0.0210,0.0083</t>
+  </si>
+  <si>
+    <t>0.9454,0.0182,0.0093,0.0050</t>
+  </si>
+  <si>
+    <t>0.9437,0.0152,0.0234,0.0053</t>
+  </si>
+  <si>
+    <t>0.9467,0.0117,0.0105,0.0066</t>
+  </si>
+  <si>
+    <t>0.9444,0.0130,0.0109,0.0073</t>
+  </si>
+  <si>
+    <t>0.9292,0.0196,0.0149,0.0076</t>
+  </si>
+  <si>
+    <t>0.9426,0.0167,0.0132,0.0064</t>
+  </si>
+  <si>
+    <t>0.9492,0.0106,0.0093,0.0067</t>
+  </si>
+  <si>
+    <t>0.9393,0.0134,0.0077,0.0063</t>
+  </si>
+  <si>
+    <t>0.1407,0.0199,0.9120,0.0011</t>
+  </si>
+  <si>
+    <t>0.7144,0.0623,0.2339,0.0035</t>
+  </si>
+  <si>
+    <t>0.8364,0.0395,0.1378,0.0036</t>
+  </si>
+  <si>
+    <t>0.7619,0.0438,0.2470,0.0036</t>
+  </si>
+  <si>
+    <t>0.7019,0.2824,0.0368,0.0150</t>
+  </si>
+  <si>
+    <t>0.7339,0.2161,0.0715,0.0104</t>
+  </si>
+  <si>
+    <t>0.7568,0.1768,0.0497,0.0159</t>
+  </si>
+  <si>
+    <t>0.8623,0.0670,0.0298,0.0111</t>
+  </si>
+  <si>
+    <t>0.5783,0.4311,0.0527,0.0123</t>
+  </si>
+  <si>
+    <t>0.3274,0.6670,0.0673,0.0313</t>
+  </si>
+  <si>
+    <t>0.8922,0.0481,0.0396,0.0044</t>
+  </si>
+  <si>
+    <t>0.7793,0.1147,0.1189,0.0095</t>
+  </si>
+  <si>
+    <t>0.7708,0.0493,0.2333,0.0059</t>
+  </si>
+  <si>
+    <t>0.8264,0.0647,0.1391,0.0046</t>
+  </si>
+  <si>
+    <t>0.6374,0.2102,0.1996,0.0148</t>
+  </si>
+  <si>
+    <t>0.7873,0.1076,0.0692,0.0218</t>
+  </si>
+  <si>
+    <t>0.0500,0.9181,0.1453,0.0209</t>
+  </si>
+  <si>
+    <t>0.0459,0.9374,0.1138,0.0323</t>
+  </si>
+  <si>
+    <t>0.5263,0.3571,0.1173,0.0089</t>
+  </si>
+  <si>
+    <t>0.0067,0.7674,0.9384,0.0025</t>
+  </si>
+  <si>
+    <t>0.4549,0.4919,0.1949,0.0311</t>
+  </si>
+  <si>
+    <t>0.7971,0.1310,0.0478,0.0119</t>
+  </si>
+  <si>
+    <t>0.7796,0.1568,0.0331,0.0151</t>
+  </si>
+  <si>
+    <t>0.9309,0.0242,0.0168,0.0051</t>
+  </si>
+  <si>
+    <t>0.9395,0.0152,0.0182,0.0045</t>
+  </si>
+  <si>
+    <t>0.9144,0.0314,0.0262,0.0060</t>
+  </si>
+  <si>
+    <t>0.9368,0.0165,0.0085,0.0061</t>
+  </si>
+  <si>
+    <t>0.9057,0.0355,0.0194,0.0077</t>
+  </si>
+  <si>
+    <t>0.9467,0.0108,0.0302,0.0051</t>
+  </si>
+  <si>
+    <t>0.9247,0.0316,0.0214,0.0040</t>
+  </si>
+  <si>
+    <t>0.9083,0.0216,0.0392,0.0083</t>
+  </si>
+  <si>
+    <t>0.2606,0.1181,0.6743,0.0010</t>
+  </si>
+  <si>
+    <t>0.1368,0.3194,0.6344,0.0014</t>
+  </si>
+  <si>
+    <t>0.3947,0.0689,0.6283,0.0016</t>
+  </si>
+  <si>
+    <t>0.3502,0.0410,0.6504,0.0009</t>
+  </si>
+  <si>
+    <t>0.9288,0.0189,0.0457,0.0026</t>
+  </si>
+  <si>
+    <t>0.8030,0.0649,0.1497,0.0075</t>
+  </si>
+  <si>
+    <t>0.8565,0.0179,0.1796,0.0038</t>
+  </si>
+  <si>
+    <t>0.7990,0.0552,0.1678,0.0131</t>
+  </si>
+  <si>
+    <t>0.9102,0.0185,0.0465,0.0106</t>
+  </si>
+  <si>
+    <t>0.7975,0.0178,0.0358,0.0885</t>
+  </si>
+  <si>
+    <t>0.8219,0.0553,0.0679,0.0304</t>
+  </si>
+  <si>
+    <t>0.8292,0.0510,0.0966,0.0176</t>
+  </si>
+  <si>
+    <t>0.0413,0.6556,0.8087,0.0011</t>
+  </si>
+  <si>
+    <t>0.9368,0.0219,0.0067,0.0051</t>
+  </si>
+  <si>
+    <t>0.9015,0.0584,0.0215,0.0040</t>
+  </si>
+  <si>
+    <t>0.9323,0.0217,0.0172,0.0066</t>
+  </si>
+  <si>
+    <t>0.7784,0.1478,0.0551,0.0130</t>
+  </si>
+  <si>
+    <t>0.9281,0.0225,0.0275,0.0052</t>
+  </si>
+  <si>
+    <t>0.9298,0.0224,0.0469,0.0033</t>
+  </si>
+  <si>
+    <t>0.9209,0.0263,0.0192,0.0064</t>
+  </si>
+  <si>
+    <t>0.0992,0.1351,0.8857,0.0205</t>
+  </si>
+  <si>
+    <t>0.9394,0.0130,0.0354,0.0031</t>
+  </si>
+  <si>
+    <t>0.8289,0.0895,0.0547,0.0109</t>
+  </si>
+  <si>
+    <t>0.7944,0.1200,0.0651,0.0211</t>
+  </si>
+  <si>
+    <t>0.8014,0.1060,0.0721,0.0101</t>
+  </si>
+  <si>
+    <t>0.7814,0.1235,0.0644,0.0129</t>
+  </si>
+  <si>
+    <t>0.7948,0.1177,0.0913,0.0092</t>
+  </si>
+  <si>
+    <t>0.7827,0.1201,0.0648,0.0189</t>
+  </si>
+  <si>
+    <t>0.8802,0.0589,0.0391,0.0064</t>
+  </si>
+  <si>
+    <t>0.9287,0.0308,0.0113,0.0052</t>
+  </si>
+  <si>
+    <t>0.9526,0.0091,0.0251,0.0046</t>
+  </si>
+  <si>
+    <t>0.9118,0.0263,0.0196,0.0108</t>
+  </si>
+  <si>
+    <t>0.9418,0.0131,0.0325,0.0047</t>
+  </si>
+  <si>
+    <t>0.9210,0.0207,0.0149,0.0087</t>
+  </si>
+  <si>
+    <t>0.8974,0.0444,0.0272,0.0083</t>
+  </si>
+  <si>
+    <t>0.9422,0.0154,0.0231,0.0043</t>
+  </si>
+  <si>
+    <t>0.9132,0.0228,0.0155,0.0110</t>
+  </si>
+  <si>
+    <t>0.7087,0.2205,0.0573,0.0217</t>
+  </si>
+  <si>
+    <t>0.8795,0.0649,0.0261,0.0068</t>
+  </si>
+  <si>
+    <t>0.8895,0.0566,0.0224,0.0068</t>
+  </si>
+  <si>
+    <t>0.8589,0.0582,0.0952,0.0071</t>
+  </si>
+  <si>
+    <t>0.9139,0.0291,0.0258,0.0058</t>
+  </si>
+  <si>
+    <t>0.9085,0.0258,0.0215,0.0131</t>
+  </si>
+  <si>
+    <t>0.9264,0.0278,0.0268,0.0033</t>
+  </si>
+  <si>
+    <t>0.9474,0.0134,0.0105,0.0051</t>
+  </si>
+  <si>
+    <t>0.3215,0.0347,0.7628,0.0043</t>
+  </si>
+  <si>
+    <t>0.8957,0.0364,0.0224,0.0089</t>
+  </si>
+  <si>
+    <t>0.4885,0.0104,0.6857,0.0012</t>
+  </si>
+  <si>
+    <t>0.6166,0.0490,0.5004,0.0060</t>
+  </si>
+  <si>
+    <t>0.8025,0.0359,0.2410,0.0057</t>
+  </si>
+  <si>
+    <t>0.3322,0.0401,0.7484,0.0008</t>
+  </si>
+  <si>
+    <t>0.3150,0.1340,0.6612,0.0041</t>
+  </si>
+  <si>
+    <t>0.4607,0.0287,0.6486,0.0024</t>
+  </si>
+  <si>
+    <t>0.3035,0.0191,0.7806,0.0011</t>
+  </si>
+  <si>
+    <t>0.7731,0.0734,0.1875,0.0117</t>
+  </si>
+  <si>
+    <t>0.5405,0.0385,0.5329,0.0020</t>
+  </si>
+  <si>
+    <t>0.7385,0.0806,0.2039,0.0044</t>
+  </si>
+  <si>
+    <t>0.7368,0.0863,0.1641,0.0051</t>
+  </si>
+  <si>
+    <t>0.4850,0.3956,0.2447,0.0341</t>
+  </si>
+  <si>
+    <t>0.7698,0.0894,0.1519,0.0067</t>
+  </si>
+  <si>
+    <t>0.7721,0.0858,0.1482,0.0077</t>
+  </si>
+  <si>
+    <t>0.6747,0.0240,0.4104,0.0031</t>
+  </si>
+  <si>
+    <t>0.8988,0.0515,0.0197,0.0060</t>
+  </si>
+  <si>
+    <t>0.7756,0.1574,0.0539,0.0079</t>
+  </si>
+  <si>
+    <t>0.8767,0.0645,0.0305,0.0059</t>
+  </si>
+  <si>
+    <t>0.9577,0.0103,0.0097,0.0043</t>
+  </si>
+  <si>
+    <t>0.9524,0.0141,0.0134,0.0025</t>
+  </si>
+  <si>
+    <t>0.8255,0.0374,0.1533,0.0021</t>
+  </si>
+  <si>
+    <t>0.8416,0.0402,0.1511,0.0047</t>
+  </si>
+  <si>
+    <t>0.7860,0.0800,0.1434,0.0089</t>
+  </si>
+  <si>
+    <t>0.6274,0.1367,0.3247,0.0202</t>
+  </si>
+  <si>
+    <t>0.8564,0.0330,0.1067,0.0040</t>
+  </si>
+  <si>
+    <t>0.6582,0.0333,0.4268,0.0039</t>
+  </si>
+  <si>
+    <t>0.8172,0.0305,0.2156,0.0010</t>
+  </si>
+  <si>
+    <t>0.2217,0.1819,0.6806,0.0006</t>
+  </si>
+  <si>
+    <t>0.4164,0.0204,0.7032,0.0005</t>
+  </si>
+  <si>
+    <t>0.3343,0.0634,0.6563,0.0018</t>
+  </si>
+  <si>
+    <t>0.9175,0.0317,0.0196,0.0064</t>
+  </si>
+  <si>
+    <t>0.9136,0.0423,0.0158,0.0060</t>
+  </si>
+  <si>
+    <t>0.9282,0.0197,0.0107,0.0083</t>
+  </si>
+  <si>
+    <t>0.9317,0.0195,0.0125,0.0069</t>
+  </si>
+  <si>
+    <t>0.9206,0.0262,0.0259,0.0062</t>
+  </si>
+  <si>
+    <t>0.9468,0.0150,0.0162,0.0044</t>
+  </si>
+  <si>
+    <t>0.9233,0.0290,0.0197,0.0075</t>
+  </si>
+  <si>
+    <t>0.8917,0.0360,0.0215,0.0146</t>
+  </si>
+  <si>
+    <t>0.6829,0.0685,0.3492,0.0113</t>
+  </si>
+  <si>
+    <t>0.8679,0.0356,0.0898,0.0077</t>
+  </si>
+  <si>
+    <t>0.8993,0.0308,0.0334,0.0100</t>
+  </si>
+  <si>
+    <t>0.1579,0.0369,0.8489,0.0019</t>
+  </si>
+  <si>
+    <t>0.0765,0.0876,0.8776,0.0014</t>
+  </si>
+  <si>
+    <t>0.5533,0.1193,0.3886,0.0027</t>
+  </si>
+  <si>
+    <t>0.0542,0.0136,0.9700,0.0006</t>
+  </si>
+  <si>
+    <t>0.4686,0.0167,0.6458,0.0008</t>
+  </si>
+  <si>
+    <t>0.0204,0.2508,0.9707,0.0011</t>
+  </si>
+  <si>
+    <t>0.4587,0.0904,0.4406,0.0026</t>
+  </si>
+  <si>
+    <t>0.5727,0.2228,0.3029,0.0184</t>
+  </si>
+  <si>
+    <t>0.8145,0.0426,0.1869,0.0027</t>
+  </si>
+  <si>
+    <t>0.8882,0.0142,0.1294,0.0048</t>
+  </si>
+  <si>
+    <t>0.8262,0.0362,0.1519,0.0026</t>
+  </si>
+  <si>
+    <t>0.9505,0.0160,0.0076,0.0043</t>
+  </si>
+  <si>
+    <t>0.8972,0.0509,0.0251,0.0070</t>
+  </si>
+  <si>
+    <t>0.9278,0.0210,0.0213,0.0087</t>
+  </si>
+  <si>
+    <t>0.9203,0.0335,0.0239,0.0047</t>
+  </si>
+  <si>
+    <t>0.9629,0.0083,0.0078,0.0029</t>
+  </si>
+  <si>
+    <t>0.9158,0.0302,0.0300,0.0056</t>
+  </si>
+  <si>
+    <t>0.9473,0.0127,0.0108,0.0051</t>
+  </si>
+  <si>
+    <t>0.9510,0.0097,0.0080,0.0066</t>
+  </si>
+  <si>
+    <t>0.6829,0.0870,0.2305,0.0032</t>
+  </si>
+  <si>
+    <t>0.0272,0.1732,0.9395,0.0015</t>
+  </si>
+  <si>
+    <t>0.0381,0.3465,0.8790,0.0008</t>
+  </si>
+  <si>
+    <t>0.6761,0.0631,0.2820,0.0024</t>
+  </si>
+  <si>
+    <t>0.3086,0.0684,0.6987,0.0014</t>
+  </si>
+  <si>
+    <t>0.7674,0.0687,0.2078,0.0089</t>
+  </si>
+  <si>
+    <t>0.7709,0.0620,0.1375,0.0018</t>
+  </si>
+  <si>
+    <t>0.4386,0.0392,0.6213,0.0022</t>
+  </si>
+  <si>
+    <t>0.9161,0.0160,0.0494,0.0066</t>
+  </si>
+  <si>
+    <t>0.7849,0.0599,0.0793,0.0542</t>
+  </si>
+  <si>
+    <t>0.9006,0.0170,0.0550,0.0126</t>
+  </si>
+  <si>
+    <t>0.8943,0.0143,0.0320,0.0219</t>
+  </si>
+  <si>
+    <t>0.8858,0.0110,0.0276,0.0307</t>
+  </si>
+  <si>
+    <t>0.8181,0.0718,0.0681,0.0083</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
